--- a/tame_output/ON/bt/strategyON_20231017.xlsx
+++ b/tame_output/ON/bt/strategyON_20231017.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.3%</t>
+          <t>-158.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.1%</t>
+          <t>130.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1752"/>
+  <dimension ref="A1:G1753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41806,7 +41806,7 @@
         <v>45214</v>
       </c>
       <c r="B1752" t="n">
-        <v>2.817300619330886</v>
+        <v>2.817841160675789</v>
       </c>
       <c r="C1752" t="n">
         <v>2.953840430523644</v>
@@ -41822,6 +41822,29 @@
       </c>
       <c r="G1752" t="n">
         <v>4.250786581611115</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="2" t="n">
+        <v>45215</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>2.856263949404791</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>2.959094075792072</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>1.567170919392201</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>3.585606019235205</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>2.161576918479115</v>
+      </c>
+      <c r="G1753" t="n">
+        <v>4.256040226879542</v>
       </c>
     </row>
   </sheetData>
